--- a/examples/sixdrive12resp/results/case/profiles/profile_04_optdiag_capoff.xlsx
+++ b/examples/sixdrive12resp/results/case/profiles/profile_04_optdiag_capoff.xlsx
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">

--- a/examples/sixdrive12resp/results/case/profiles/profile_04_optdiag_capoff.xlsx
+++ b/examples/sixdrive12resp/results/case/profiles/profile_04_optdiag_capoff.xlsx
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
